--- a/api/tests/testthat/fixtures/surveymonkey/golden/Estudiantes_inst.xlsx
+++ b/api/tests/testthat/fixtures/surveymonkey/golden/Estudiantes_inst.xlsx
@@ -788,7 +788,7 @@
     <t xml:space="preserve">es</t>
   </si>
   <si>
-    <t xml:space="preserve">20260430</t>
+    <t xml:space="preserve">20260502</t>
   </si>
   <si>
     <t xml:space="preserve">order</t>

--- a/api/tests/testthat/fixtures/surveymonkey/golden/Estudiantes_inst.xlsx
+++ b/api/tests/testthat/fixtures/surveymonkey/golden/Estudiantes_inst.xlsx
@@ -788,7 +788,7 @@
     <t xml:space="preserve">es</t>
   </si>
   <si>
-    <t xml:space="preserve">20260502</t>
+    <t xml:space="preserve">20260523</t>
   </si>
   <si>
     <t xml:space="preserve">order</t>
@@ -1462,11 +1462,21 @@
       <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
+      <c r="D2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H2" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I2" t="s">
         <v>10</v>
       </c>
@@ -1481,11 +1491,21 @@
       <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
+      <c r="D3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H3" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I3" t="s">
         <v>10</v>
       </c>
@@ -1494,13 +1514,27 @@
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
+      <c r="B4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H4" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I4" t="s">
         <v>10</v>
       </c>
@@ -1515,11 +1549,21 @@
       <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
+      <c r="D5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H5" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I5" t="s">
         <v>15</v>
       </c>
@@ -1534,11 +1578,21 @@
       <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
+      <c r="D6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I6" t="s">
         <v>15</v>
       </c>
@@ -1547,13 +1601,27 @@
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7"/>
+      <c r="B7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H7" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I7" t="s">
         <v>15</v>
       </c>
@@ -1568,11 +1636,21 @@
       <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
+      <c r="D8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H8" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I8" t="s">
         <v>23</v>
       </c>
@@ -1587,11 +1665,21 @@
       <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
+      <c r="D9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H9" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I9" t="s">
         <v>23</v>
       </c>
@@ -1606,11 +1694,21 @@
       <c r="C10" t="s">
         <v>28</v>
       </c>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10"/>
+      <c r="D10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H10" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I10" t="s">
         <v>23</v>
       </c>
@@ -1625,11 +1723,21 @@
       <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
+      <c r="D11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H11" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I11" t="s">
         <v>23</v>
       </c>
@@ -1644,11 +1752,21 @@
       <c r="C12" t="s">
         <v>16</v>
       </c>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
+      <c r="D12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H12" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I12" t="s">
         <v>15</v>
       </c>
@@ -1663,11 +1781,21 @@
       <c r="C13" t="s">
         <v>33</v>
       </c>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
+      <c r="D13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H13" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I13" t="s">
         <v>15</v>
       </c>
@@ -1676,13 +1804,27 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
+      <c r="B14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H14" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I14" t="s">
         <v>15</v>
       </c>
@@ -1697,11 +1839,21 @@
       <c r="C15" t="s">
         <v>36</v>
       </c>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
+      <c r="D15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H15" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I15" t="s">
         <v>23</v>
       </c>
@@ -1716,11 +1868,21 @@
       <c r="C16" t="s">
         <v>38</v>
       </c>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
+      <c r="D16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H16" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I16" t="s">
         <v>39</v>
       </c>
@@ -1735,11 +1897,21 @@
       <c r="C17" t="s">
         <v>38</v>
       </c>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
+      <c r="D17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H17" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I17" t="s">
         <v>39</v>
       </c>
@@ -1754,11 +1926,21 @@
       <c r="C18" t="s">
         <v>42</v>
       </c>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18"/>
-      <c r="H18"/>
+      <c r="D18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H18" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I18" t="s">
         <v>39</v>
       </c>
@@ -1773,11 +1955,21 @@
       <c r="C19" t="s">
         <v>44</v>
       </c>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
+      <c r="D19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H19" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I19" t="s">
         <v>39</v>
       </c>
@@ -1786,13 +1978,27 @@
       <c r="A20" t="s">
         <v>14</v>
       </c>
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
+      <c r="B20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H20" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I20" t="s">
         <v>39</v>
       </c>
@@ -1807,11 +2013,21 @@
       <c r="C21" t="s">
         <v>47</v>
       </c>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
+      <c r="D21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H21" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I21" t="s">
         <v>23</v>
       </c>
@@ -1823,12 +2039,24 @@
       <c r="B22" t="s">
         <v>48</v>
       </c>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
+      <c r="C22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H22" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I22" t="s">
         <v>49</v>
       </c>
@@ -1843,11 +2071,21 @@
       <c r="C23" t="s">
         <v>52</v>
       </c>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
+      <c r="D23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H23" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I23" t="s">
         <v>49</v>
       </c>
@@ -1862,11 +2100,21 @@
       <c r="C24" t="s">
         <v>54</v>
       </c>
-      <c r="D24"/>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
+      <c r="D24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H24" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I24" t="s">
         <v>49</v>
       </c>
@@ -1881,11 +2129,21 @@
       <c r="C25" t="s">
         <v>56</v>
       </c>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
+      <c r="D25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H25" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I25" t="s">
         <v>49</v>
       </c>
@@ -1900,11 +2158,21 @@
       <c r="C26" t="s">
         <v>58</v>
       </c>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
+      <c r="D26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H26" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I26" t="s">
         <v>49</v>
       </c>
@@ -1919,11 +2187,21 @@
       <c r="C27" t="s">
         <v>60</v>
       </c>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27"/>
+      <c r="D27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H27" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I27" t="s">
         <v>49</v>
       </c>
@@ -1938,11 +2216,21 @@
       <c r="C28" t="s">
         <v>62</v>
       </c>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
+      <c r="D28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H28" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I28" t="s">
         <v>49</v>
       </c>
@@ -1951,13 +2239,27 @@
       <c r="A29" t="s">
         <v>14</v>
       </c>
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-      <c r="H29"/>
+      <c r="B29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H29" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I29" t="s">
         <v>49</v>
       </c>
@@ -1969,12 +2271,24 @@
       <c r="B30" t="s">
         <v>63</v>
       </c>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
+      <c r="C30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H30" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I30" t="s">
         <v>64</v>
       </c>
@@ -1989,11 +2303,21 @@
       <c r="C31" t="s">
         <v>66</v>
       </c>
-      <c r="D31"/>
-      <c r="E31"/>
-      <c r="F31"/>
-      <c r="G31"/>
-      <c r="H31"/>
+      <c r="D31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H31" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I31" t="s">
         <v>64</v>
       </c>
@@ -2008,11 +2332,21 @@
       <c r="C32" t="s">
         <v>68</v>
       </c>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-      <c r="H32"/>
+      <c r="D32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H32" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I32" t="s">
         <v>64</v>
       </c>
@@ -2027,11 +2361,21 @@
       <c r="C33" t="s">
         <v>70</v>
       </c>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33"/>
-      <c r="H33"/>
+      <c r="D33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H33" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I33" t="s">
         <v>64</v>
       </c>
@@ -2046,11 +2390,21 @@
       <c r="C34" t="s">
         <v>72</v>
       </c>
-      <c r="D34"/>
-      <c r="E34"/>
-      <c r="F34"/>
-      <c r="G34"/>
-      <c r="H34"/>
+      <c r="D34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H34" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I34" t="s">
         <v>64</v>
       </c>
@@ -2065,11 +2419,21 @@
       <c r="C35" t="s">
         <v>74</v>
       </c>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
+      <c r="D35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H35" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I35" t="s">
         <v>64</v>
       </c>
@@ -2084,11 +2448,21 @@
       <c r="C36" t="s">
         <v>76</v>
       </c>
-      <c r="D36"/>
-      <c r="E36"/>
-      <c r="F36"/>
-      <c r="G36"/>
-      <c r="H36"/>
+      <c r="D36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H36" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I36" t="s">
         <v>64</v>
       </c>
@@ -2097,13 +2471,27 @@
       <c r="A37" t="s">
         <v>14</v>
       </c>
-      <c r="B37"/>
-      <c r="C37"/>
-      <c r="D37"/>
-      <c r="E37"/>
-      <c r="F37"/>
-      <c r="G37"/>
-      <c r="H37"/>
+      <c r="B37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H37" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I37" t="s">
         <v>64</v>
       </c>
@@ -2118,11 +2506,21 @@
       <c r="C38" t="s">
         <v>78</v>
       </c>
-      <c r="D38"/>
-      <c r="E38"/>
-      <c r="F38"/>
-      <c r="G38"/>
-      <c r="H38"/>
+      <c r="D38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H38" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I38" t="s">
         <v>23</v>
       </c>
@@ -2134,12 +2532,24 @@
       <c r="B39" t="s">
         <v>79</v>
       </c>
-      <c r="C39"/>
-      <c r="D39"/>
-      <c r="E39"/>
-      <c r="F39"/>
-      <c r="G39"/>
-      <c r="H39"/>
+      <c r="C39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H39" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I39" t="s">
         <v>80</v>
       </c>
@@ -2154,11 +2564,21 @@
       <c r="C40" t="s">
         <v>82</v>
       </c>
-      <c r="D40"/>
-      <c r="E40"/>
-      <c r="F40"/>
-      <c r="G40"/>
-      <c r="H40"/>
+      <c r="D40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H40" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I40" t="s">
         <v>80</v>
       </c>
@@ -2173,11 +2593,21 @@
       <c r="C41" t="s">
         <v>84</v>
       </c>
-      <c r="D41"/>
-      <c r="E41"/>
-      <c r="F41"/>
-      <c r="G41"/>
-      <c r="H41"/>
+      <c r="D41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H41" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I41" t="s">
         <v>80</v>
       </c>
@@ -2186,13 +2616,27 @@
       <c r="A42" t="s">
         <v>14</v>
       </c>
-      <c r="B42"/>
-      <c r="C42"/>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
+      <c r="B42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H42" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I42" t="s">
         <v>80</v>
       </c>
@@ -2207,11 +2651,21 @@
       <c r="C43" t="s">
         <v>86</v>
       </c>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43"/>
+      <c r="D43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H43" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I43" t="s">
         <v>23</v>
       </c>
@@ -2223,12 +2677,24 @@
       <c r="B44" t="s">
         <v>87</v>
       </c>
-      <c r="C44"/>
-      <c r="D44"/>
-      <c r="E44"/>
-      <c r="F44"/>
-      <c r="G44"/>
-      <c r="H44"/>
+      <c r="C44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H44" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I44" t="s">
         <v>88</v>
       </c>
@@ -2243,11 +2709,21 @@
       <c r="C45" t="s">
         <v>90</v>
       </c>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
+      <c r="D45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H45" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I45" t="s">
         <v>88</v>
       </c>
@@ -2262,11 +2738,21 @@
       <c r="C46" t="s">
         <v>92</v>
       </c>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46"/>
-      <c r="G46"/>
-      <c r="H46"/>
+      <c r="D46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H46" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I46" t="s">
         <v>88</v>
       </c>
@@ -2281,11 +2767,21 @@
       <c r="C47" t="s">
         <v>94</v>
       </c>
-      <c r="D47"/>
-      <c r="E47"/>
-      <c r="F47"/>
-      <c r="G47"/>
-      <c r="H47"/>
+      <c r="D47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H47" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I47" t="s">
         <v>88</v>
       </c>
@@ -2300,11 +2796,21 @@
       <c r="C48" t="s">
         <v>96</v>
       </c>
-      <c r="D48"/>
-      <c r="E48"/>
-      <c r="F48"/>
-      <c r="G48"/>
-      <c r="H48"/>
+      <c r="D48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H48" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I48" t="s">
         <v>88</v>
       </c>
@@ -2319,11 +2825,21 @@
       <c r="C49" t="s">
         <v>98</v>
       </c>
-      <c r="D49"/>
-      <c r="E49"/>
-      <c r="F49"/>
-      <c r="G49"/>
-      <c r="H49"/>
+      <c r="D49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H49" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I49" t="s">
         <v>88</v>
       </c>
@@ -2332,13 +2848,27 @@
       <c r="A50" t="s">
         <v>14</v>
       </c>
-      <c r="B50"/>
-      <c r="C50"/>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50"/>
-      <c r="G50"/>
-      <c r="H50"/>
+      <c r="B50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H50" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I50" t="s">
         <v>88</v>
       </c>
@@ -2350,12 +2880,24 @@
       <c r="B51" t="s">
         <v>99</v>
       </c>
-      <c r="C51"/>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51"/>
-      <c r="G51"/>
-      <c r="H51"/>
+      <c r="C51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H51" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I51" t="s">
         <v>100</v>
       </c>
@@ -2370,11 +2912,21 @@
       <c r="C52" t="s">
         <v>102</v>
       </c>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
-      <c r="H52"/>
+      <c r="D52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H52" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I52" t="s">
         <v>100</v>
       </c>
@@ -2389,11 +2941,21 @@
       <c r="C53" t="s">
         <v>104</v>
       </c>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
+      <c r="D53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H53" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I53" t="s">
         <v>100</v>
       </c>
@@ -2408,11 +2970,21 @@
       <c r="C54" t="s">
         <v>106</v>
       </c>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
+      <c r="D54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H54" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I54" t="s">
         <v>100</v>
       </c>
@@ -2427,11 +2999,21 @@
       <c r="C55" t="s">
         <v>108</v>
       </c>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
+      <c r="D55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H55" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I55" t="s">
         <v>100</v>
       </c>
@@ -2446,11 +3028,21 @@
       <c r="C56" t="s">
         <v>110</v>
       </c>
-      <c r="D56"/>
-      <c r="E56"/>
-      <c r="F56"/>
-      <c r="G56"/>
-      <c r="H56"/>
+      <c r="D56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H56" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I56" t="s">
         <v>100</v>
       </c>
@@ -2459,13 +3051,27 @@
       <c r="A57" t="s">
         <v>14</v>
       </c>
-      <c r="B57"/>
-      <c r="C57"/>
-      <c r="D57"/>
-      <c r="E57"/>
-      <c r="F57"/>
-      <c r="G57"/>
-      <c r="H57"/>
+      <c r="B57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H57" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I57" t="s">
         <v>100</v>
       </c>
@@ -2480,11 +3086,21 @@
       <c r="C58" t="s">
         <v>112</v>
       </c>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
-      <c r="G58"/>
-      <c r="H58"/>
+      <c r="D58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H58" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I58" t="s">
         <v>23</v>
       </c>
@@ -2496,12 +3112,24 @@
       <c r="B59" t="s">
         <v>113</v>
       </c>
-      <c r="C59"/>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
-      <c r="G59"/>
-      <c r="H59"/>
+      <c r="C59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H59" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I59" t="s">
         <v>114</v>
       </c>
@@ -2516,11 +3144,21 @@
       <c r="C60" t="s">
         <v>116</v>
       </c>
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60"/>
-      <c r="G60"/>
-      <c r="H60"/>
+      <c r="D60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H60" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I60" t="s">
         <v>114</v>
       </c>
@@ -2535,11 +3173,21 @@
       <c r="C61" t="s">
         <v>118</v>
       </c>
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61"/>
-      <c r="G61"/>
-      <c r="H61"/>
+      <c r="D61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H61" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I61" t="s">
         <v>114</v>
       </c>
@@ -2548,13 +3196,27 @@
       <c r="A62" t="s">
         <v>14</v>
       </c>
-      <c r="B62"/>
-      <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="H62"/>
+      <c r="B62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H62" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I62" t="s">
         <v>114</v>
       </c>
@@ -2566,12 +3228,24 @@
       <c r="B63" t="s">
         <v>119</v>
       </c>
-      <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
-      <c r="G63"/>
-      <c r="H63"/>
+      <c r="C63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H63" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I63" t="s">
         <v>120</v>
       </c>
@@ -2586,11 +3260,21 @@
       <c r="C64" t="s">
         <v>122</v>
       </c>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
-      <c r="H64"/>
+      <c r="D64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H64" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I64" t="s">
         <v>120</v>
       </c>
@@ -2605,11 +3289,21 @@
       <c r="C65" t="s">
         <v>124</v>
       </c>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
-      <c r="G65"/>
-      <c r="H65"/>
+      <c r="D65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H65" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I65" t="s">
         <v>120</v>
       </c>
@@ -2624,11 +3318,21 @@
       <c r="C66" t="s">
         <v>126</v>
       </c>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
-      <c r="G66"/>
-      <c r="H66"/>
+      <c r="D66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H66" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I66" t="s">
         <v>120</v>
       </c>
@@ -2643,11 +3347,21 @@
       <c r="C67" t="s">
         <v>128</v>
       </c>
-      <c r="D67"/>
-      <c r="E67"/>
-      <c r="F67"/>
-      <c r="G67"/>
-      <c r="H67"/>
+      <c r="D67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H67" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I67" t="s">
         <v>120</v>
       </c>
@@ -2662,11 +3376,21 @@
       <c r="C68" t="s">
         <v>130</v>
       </c>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
-      <c r="G68"/>
-      <c r="H68"/>
+      <c r="D68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H68" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I68" t="s">
         <v>120</v>
       </c>
@@ -2681,11 +3405,21 @@
       <c r="C69" t="s">
         <v>132</v>
       </c>
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69"/>
-      <c r="G69"/>
-      <c r="H69"/>
+      <c r="D69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H69" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I69" t="s">
         <v>120</v>
       </c>
@@ -2700,11 +3434,21 @@
       <c r="C70" t="s">
         <v>134</v>
       </c>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
-      <c r="G70"/>
-      <c r="H70"/>
+      <c r="D70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H70" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I70" t="s">
         <v>120</v>
       </c>
@@ -2713,13 +3457,27 @@
       <c r="A71" t="s">
         <v>14</v>
       </c>
-      <c r="B71"/>
-      <c r="C71"/>
-      <c r="D71"/>
-      <c r="E71"/>
-      <c r="F71"/>
-      <c r="G71"/>
-      <c r="H71"/>
+      <c r="B71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H71" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I71" t="s">
         <v>120</v>
       </c>
@@ -2734,11 +3492,21 @@
       <c r="C72" t="s">
         <v>136</v>
       </c>
-      <c r="D72"/>
-      <c r="E72"/>
-      <c r="F72"/>
-      <c r="G72"/>
-      <c r="H72"/>
+      <c r="D72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H72" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I72" t="s">
         <v>23</v>
       </c>
@@ -2750,12 +3518,24 @@
       <c r="B73" t="s">
         <v>137</v>
       </c>
-      <c r="C73"/>
-      <c r="D73"/>
-      <c r="E73"/>
-      <c r="F73"/>
-      <c r="G73"/>
-      <c r="H73"/>
+      <c r="C73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H73" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I73" t="s">
         <v>138</v>
       </c>
@@ -2770,11 +3550,21 @@
       <c r="C74" t="s">
         <v>140</v>
       </c>
-      <c r="D74"/>
-      <c r="E74"/>
-      <c r="F74"/>
-      <c r="G74"/>
-      <c r="H74"/>
+      <c r="D74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H74" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I74" t="s">
         <v>138</v>
       </c>
@@ -2789,11 +3579,21 @@
       <c r="C75" t="s">
         <v>142</v>
       </c>
-      <c r="D75"/>
-      <c r="E75"/>
-      <c r="F75"/>
-      <c r="G75"/>
-      <c r="H75"/>
+      <c r="D75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H75" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I75" t="s">
         <v>138</v>
       </c>
@@ -2808,11 +3608,21 @@
       <c r="C76" t="s">
         <v>144</v>
       </c>
-      <c r="D76"/>
-      <c r="E76"/>
-      <c r="F76"/>
-      <c r="G76"/>
-      <c r="H76"/>
+      <c r="D76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H76" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I76" t="s">
         <v>138</v>
       </c>
@@ -2827,11 +3637,21 @@
       <c r="C77" t="s">
         <v>146</v>
       </c>
-      <c r="D77"/>
-      <c r="E77"/>
-      <c r="F77"/>
-      <c r="G77"/>
-      <c r="H77"/>
+      <c r="D77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H77" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I77" t="s">
         <v>138</v>
       </c>
@@ -2840,13 +3660,27 @@
       <c r="A78" t="s">
         <v>14</v>
       </c>
-      <c r="B78"/>
-      <c r="C78"/>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
-      <c r="G78"/>
-      <c r="H78"/>
+      <c r="B78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H78" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I78" t="s">
         <v>138</v>
       </c>
@@ -2858,12 +3692,24 @@
       <c r="B79" t="s">
         <v>147</v>
       </c>
-      <c r="C79"/>
-      <c r="D79"/>
-      <c r="E79"/>
-      <c r="F79"/>
-      <c r="G79"/>
-      <c r="H79"/>
+      <c r="C79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H79" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I79" t="s">
         <v>148</v>
       </c>
@@ -2878,11 +3724,21 @@
       <c r="C80" t="s">
         <v>150</v>
       </c>
-      <c r="D80"/>
-      <c r="E80"/>
-      <c r="F80"/>
-      <c r="G80"/>
-      <c r="H80"/>
+      <c r="D80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H80" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I80" t="s">
         <v>148</v>
       </c>
@@ -2897,11 +3753,21 @@
       <c r="C81" t="s">
         <v>152</v>
       </c>
-      <c r="D81"/>
-      <c r="E81"/>
-      <c r="F81"/>
-      <c r="G81"/>
-      <c r="H81"/>
+      <c r="D81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H81" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I81" t="s">
         <v>148</v>
       </c>
@@ -2910,13 +3776,27 @@
       <c r="A82" t="s">
         <v>14</v>
       </c>
-      <c r="B82"/>
-      <c r="C82"/>
-      <c r="D82"/>
-      <c r="E82"/>
-      <c r="F82"/>
-      <c r="G82"/>
-      <c r="H82"/>
+      <c r="B82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H82" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I82" t="s">
         <v>148</v>
       </c>
@@ -2928,12 +3808,24 @@
       <c r="B83" t="s">
         <v>153</v>
       </c>
-      <c r="C83"/>
-      <c r="D83"/>
-      <c r="E83"/>
-      <c r="F83"/>
-      <c r="G83"/>
-      <c r="H83"/>
+      <c r="C83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H83" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I83" t="s">
         <v>154</v>
       </c>
@@ -2948,11 +3840,21 @@
       <c r="C84" t="s">
         <v>156</v>
       </c>
-      <c r="D84"/>
-      <c r="E84"/>
-      <c r="F84"/>
-      <c r="G84"/>
-      <c r="H84"/>
+      <c r="D84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H84" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I84" t="s">
         <v>154</v>
       </c>
@@ -2967,11 +3869,21 @@
       <c r="C85" t="s">
         <v>158</v>
       </c>
-      <c r="D85"/>
-      <c r="E85"/>
-      <c r="F85"/>
-      <c r="G85"/>
-      <c r="H85"/>
+      <c r="D85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H85" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I85" t="s">
         <v>154</v>
       </c>
@@ -2986,11 +3898,21 @@
       <c r="C86" t="s">
         <v>160</v>
       </c>
-      <c r="D86"/>
-      <c r="E86"/>
-      <c r="F86"/>
-      <c r="G86"/>
-      <c r="H86"/>
+      <c r="D86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H86" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I86" t="s">
         <v>154</v>
       </c>
@@ -3005,11 +3927,21 @@
       <c r="C87" t="s">
         <v>162</v>
       </c>
-      <c r="D87"/>
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="G87"/>
-      <c r="H87"/>
+      <c r="D87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H87" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I87" t="s">
         <v>154</v>
       </c>
@@ -3024,11 +3956,21 @@
       <c r="C88" t="s">
         <v>164</v>
       </c>
-      <c r="D88"/>
-      <c r="E88"/>
-      <c r="F88"/>
-      <c r="G88"/>
-      <c r="H88"/>
+      <c r="D88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H88" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I88" t="s">
         <v>154</v>
       </c>
@@ -3043,11 +3985,21 @@
       <c r="C89" t="s">
         <v>166</v>
       </c>
-      <c r="D89"/>
-      <c r="E89"/>
-      <c r="F89"/>
-      <c r="G89"/>
-      <c r="H89"/>
+      <c r="D89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H89" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I89" t="s">
         <v>154</v>
       </c>
@@ -3062,11 +4014,21 @@
       <c r="C90" t="s">
         <v>168</v>
       </c>
-      <c r="D90"/>
-      <c r="E90"/>
-      <c r="F90"/>
-      <c r="G90"/>
-      <c r="H90"/>
+      <c r="D90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H90" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I90" t="s">
         <v>154</v>
       </c>
@@ -3075,13 +4037,27 @@
       <c r="A91" t="s">
         <v>14</v>
       </c>
-      <c r="B91"/>
-      <c r="C91"/>
-      <c r="D91"/>
-      <c r="E91"/>
-      <c r="F91"/>
-      <c r="G91"/>
-      <c r="H91"/>
+      <c r="B91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H91" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I91" t="s">
         <v>154</v>
       </c>
@@ -3093,12 +4069,24 @@
       <c r="B92" t="s">
         <v>169</v>
       </c>
-      <c r="C92"/>
-      <c r="D92"/>
-      <c r="E92"/>
-      <c r="F92"/>
-      <c r="G92"/>
-      <c r="H92"/>
+      <c r="C92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H92" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I92" t="s">
         <v>170</v>
       </c>
@@ -3113,11 +4101,21 @@
       <c r="C93" t="s">
         <v>172</v>
       </c>
-      <c r="D93"/>
-      <c r="E93"/>
-      <c r="F93"/>
-      <c r="G93"/>
-      <c r="H93"/>
+      <c r="D93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H93" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I93" t="s">
         <v>170</v>
       </c>
@@ -3132,11 +4130,21 @@
       <c r="C94" t="s">
         <v>174</v>
       </c>
-      <c r="D94"/>
-      <c r="E94"/>
-      <c r="F94"/>
-      <c r="G94"/>
-      <c r="H94"/>
+      <c r="D94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H94" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I94" t="s">
         <v>170</v>
       </c>
@@ -3151,11 +4159,21 @@
       <c r="C95" t="s">
         <v>176</v>
       </c>
-      <c r="D95"/>
-      <c r="E95"/>
-      <c r="F95"/>
-      <c r="G95"/>
-      <c r="H95"/>
+      <c r="D95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H95" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I95" t="s">
         <v>170</v>
       </c>
@@ -3170,11 +4188,21 @@
       <c r="C96" t="s">
         <v>178</v>
       </c>
-      <c r="D96"/>
-      <c r="E96"/>
-      <c r="F96"/>
-      <c r="G96"/>
-      <c r="H96"/>
+      <c r="D96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H96" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I96" t="s">
         <v>170</v>
       </c>
@@ -3183,13 +4211,27 @@
       <c r="A97" t="s">
         <v>14</v>
       </c>
-      <c r="B97"/>
-      <c r="C97"/>
-      <c r="D97"/>
-      <c r="E97"/>
-      <c r="F97"/>
-      <c r="G97"/>
-      <c r="H97"/>
+      <c r="B97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H97" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I97" t="s">
         <v>170</v>
       </c>
@@ -3204,11 +4246,21 @@
       <c r="C98" t="s">
         <v>180</v>
       </c>
-      <c r="D98"/>
-      <c r="E98"/>
-      <c r="F98"/>
-      <c r="G98"/>
-      <c r="H98"/>
+      <c r="D98" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E98" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F98" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G98" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H98" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I98" t="s">
         <v>23</v>
       </c>
@@ -3223,11 +4275,21 @@
       <c r="C99" t="s">
         <v>182</v>
       </c>
-      <c r="D99"/>
-      <c r="E99"/>
-      <c r="F99"/>
-      <c r="G99"/>
-      <c r="H99"/>
+      <c r="D99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H99" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I99" t="s">
         <v>23</v>
       </c>
@@ -3239,12 +4301,24 @@
       <c r="B100" t="s">
         <v>183</v>
       </c>
-      <c r="C100"/>
-      <c r="D100"/>
-      <c r="E100"/>
-      <c r="F100"/>
-      <c r="G100"/>
-      <c r="H100"/>
+      <c r="C100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H100" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I100" t="s">
         <v>184</v>
       </c>
@@ -3259,11 +4333,21 @@
       <c r="C101" t="s">
         <v>186</v>
       </c>
-      <c r="D101"/>
-      <c r="E101"/>
-      <c r="F101"/>
-      <c r="G101"/>
-      <c r="H101"/>
+      <c r="D101" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E101" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F101" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G101" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H101" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I101" t="s">
         <v>184</v>
       </c>
@@ -3278,11 +4362,21 @@
       <c r="C102" t="s">
         <v>188</v>
       </c>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102"/>
-      <c r="H102"/>
+      <c r="D102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H102" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I102" t="s">
         <v>184</v>
       </c>
@@ -3297,11 +4391,21 @@
       <c r="C103" t="s">
         <v>190</v>
       </c>
-      <c r="D103"/>
-      <c r="E103"/>
-      <c r="F103"/>
-      <c r="G103"/>
-      <c r="H103"/>
+      <c r="D103" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E103" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F103" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G103" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H103" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I103" t="s">
         <v>184</v>
       </c>
@@ -3316,11 +4420,21 @@
       <c r="C104" t="s">
         <v>192</v>
       </c>
-      <c r="D104"/>
-      <c r="E104"/>
-      <c r="F104"/>
-      <c r="G104"/>
-      <c r="H104"/>
+      <c r="D104" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E104" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F104" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G104" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H104" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I104" t="s">
         <v>184</v>
       </c>
@@ -3329,13 +4443,27 @@
       <c r="A105" t="s">
         <v>14</v>
       </c>
-      <c r="B105"/>
-      <c r="C105"/>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
-      <c r="G105"/>
-      <c r="H105"/>
+      <c r="B105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H105" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I105" t="s">
         <v>184</v>
       </c>
@@ -3347,12 +4475,24 @@
       <c r="B106" t="s">
         <v>193</v>
       </c>
-      <c r="C106"/>
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
-      <c r="G106"/>
-      <c r="H106"/>
+      <c r="C106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H106" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I106" t="s">
         <v>194</v>
       </c>
@@ -3367,11 +4507,21 @@
       <c r="C107" t="s">
         <v>196</v>
       </c>
-      <c r="D107"/>
-      <c r="E107"/>
-      <c r="F107"/>
-      <c r="G107"/>
-      <c r="H107"/>
+      <c r="D107" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E107" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F107" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G107" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H107" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I107" t="s">
         <v>194</v>
       </c>
@@ -3386,11 +4536,21 @@
       <c r="C108" t="s">
         <v>198</v>
       </c>
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
-      <c r="G108"/>
-      <c r="H108"/>
+      <c r="D108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H108" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I108" t="s">
         <v>194</v>
       </c>
@@ -3405,11 +4565,21 @@
       <c r="C109" t="s">
         <v>200</v>
       </c>
-      <c r="D109"/>
-      <c r="E109"/>
-      <c r="F109"/>
-      <c r="G109"/>
-      <c r="H109"/>
+      <c r="D109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H109" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I109" t="s">
         <v>194</v>
       </c>
@@ -3424,11 +4594,21 @@
       <c r="C110" t="s">
         <v>202</v>
       </c>
-      <c r="D110"/>
-      <c r="E110"/>
-      <c r="F110"/>
-      <c r="G110"/>
-      <c r="H110"/>
+      <c r="D110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H110" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I110" t="s">
         <v>194</v>
       </c>
@@ -3443,11 +4623,21 @@
       <c r="C111" t="s">
         <v>204</v>
       </c>
-      <c r="D111"/>
-      <c r="E111"/>
-      <c r="F111"/>
-      <c r="G111"/>
-      <c r="H111"/>
+      <c r="D111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H111" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I111" t="s">
         <v>194</v>
       </c>
@@ -3456,13 +4646,27 @@
       <c r="A112" t="s">
         <v>14</v>
       </c>
-      <c r="B112"/>
-      <c r="C112"/>
-      <c r="D112"/>
-      <c r="E112"/>
-      <c r="F112"/>
-      <c r="G112"/>
-      <c r="H112"/>
+      <c r="B112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H112" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I112" t="s">
         <v>194</v>
       </c>
@@ -3477,11 +4681,21 @@
       <c r="C113" t="s">
         <v>16</v>
       </c>
-      <c r="D113"/>
-      <c r="E113"/>
-      <c r="F113"/>
-      <c r="G113"/>
-      <c r="H113"/>
+      <c r="D113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H113" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I113" t="s">
         <v>15</v>
       </c>
@@ -3496,11 +4710,21 @@
       <c r="C114" t="s">
         <v>207</v>
       </c>
-      <c r="D114"/>
-      <c r="E114"/>
-      <c r="F114"/>
-      <c r="G114"/>
-      <c r="H114"/>
+      <c r="D114" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E114" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F114" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G114" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H114" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I114" t="s">
         <v>15</v>
       </c>
@@ -3509,13 +4733,27 @@
       <c r="A115" t="s">
         <v>14</v>
       </c>
-      <c r="B115"/>
-      <c r="C115"/>
-      <c r="D115"/>
-      <c r="E115"/>
-      <c r="F115"/>
-      <c r="G115"/>
-      <c r="H115"/>
+      <c r="B115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H115" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="I115" t="s">
         <v>15</v>
       </c>
@@ -3962,7 +5200,9 @@
       <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="I2"/>
+      <c r="I2" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J2" t="s">
         <v>10</v>
       </c>
@@ -3987,8 +5227,12 @@
       <c r="Q2" t="s">
         <v>278</v>
       </c>
-      <c r="R2"/>
-      <c r="S2"/>
+      <c r="R2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S2" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4003,7 +5247,9 @@
       <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="E3"/>
+      <c r="E3" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="F3" t="s">
         <v>279</v>
       </c>
@@ -4040,8 +5286,12 @@
       <c r="Q3" t="s">
         <v>278</v>
       </c>
-      <c r="R3"/>
-      <c r="S3"/>
+      <c r="R3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S3" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4095,8 +5345,12 @@
       <c r="Q4" t="s">
         <v>281</v>
       </c>
-      <c r="R4"/>
-      <c r="S4"/>
+      <c r="R4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S4" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4123,7 +5377,9 @@
       <c r="H5" t="s">
         <v>24</v>
       </c>
-      <c r="I5"/>
+      <c r="I5" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J5" t="s">
         <v>23</v>
       </c>
@@ -4148,8 +5404,12 @@
       <c r="Q5" t="s">
         <v>283</v>
       </c>
-      <c r="R5"/>
-      <c r="S5"/>
+      <c r="R5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S5" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4176,7 +5436,9 @@
       <c r="H6" t="s">
         <v>12</v>
       </c>
-      <c r="I6"/>
+      <c r="I6" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J6" t="s">
         <v>23</v>
       </c>
@@ -4201,8 +5463,12 @@
       <c r="Q6" t="s">
         <v>278</v>
       </c>
-      <c r="R6"/>
-      <c r="S6"/>
+      <c r="R6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S6" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4229,7 +5495,9 @@
       <c r="H7" t="s">
         <v>24</v>
       </c>
-      <c r="I7"/>
+      <c r="I7" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J7" t="s">
         <v>23</v>
       </c>
@@ -4254,8 +5522,12 @@
       <c r="Q7" t="s">
         <v>283</v>
       </c>
-      <c r="R7"/>
-      <c r="S7"/>
+      <c r="R7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S7" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4309,8 +5581,12 @@
       <c r="Q8" t="s">
         <v>281</v>
       </c>
-      <c r="R8"/>
-      <c r="S8"/>
+      <c r="R8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S8" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4364,8 +5640,12 @@
       <c r="Q9" t="s">
         <v>281</v>
       </c>
-      <c r="R9"/>
-      <c r="S9"/>
+      <c r="R9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S9" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4419,8 +5699,12 @@
       <c r="Q10" t="s">
         <v>281</v>
       </c>
-      <c r="R10"/>
-      <c r="S10"/>
+      <c r="R10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S10" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4474,8 +5758,12 @@
       <c r="Q11" t="s">
         <v>281</v>
       </c>
-      <c r="R11"/>
-      <c r="S11"/>
+      <c r="R11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S11" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4529,8 +5817,12 @@
       <c r="Q12" t="s">
         <v>281</v>
       </c>
-      <c r="R12"/>
-      <c r="S12"/>
+      <c r="R12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S12" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4584,8 +5876,12 @@
       <c r="Q13" t="s">
         <v>281</v>
       </c>
-      <c r="R13"/>
-      <c r="S13"/>
+      <c r="R13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S13" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4639,8 +5935,12 @@
       <c r="Q14" t="s">
         <v>281</v>
       </c>
-      <c r="R14"/>
-      <c r="S14"/>
+      <c r="R14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S14" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4694,8 +5994,12 @@
       <c r="Q15" t="s">
         <v>281</v>
       </c>
-      <c r="R15"/>
-      <c r="S15"/>
+      <c r="R15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S15" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4749,8 +6053,12 @@
       <c r="Q16" t="s">
         <v>281</v>
       </c>
-      <c r="R16"/>
-      <c r="S16"/>
+      <c r="R16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S16" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4804,8 +6112,12 @@
       <c r="Q17" t="s">
         <v>281</v>
       </c>
-      <c r="R17"/>
-      <c r="S17"/>
+      <c r="R17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S17" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4859,8 +6171,12 @@
       <c r="Q18" t="s">
         <v>281</v>
       </c>
-      <c r="R18"/>
-      <c r="S18"/>
+      <c r="R18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S18" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4914,8 +6230,12 @@
       <c r="Q19" t="s">
         <v>281</v>
       </c>
-      <c r="R19"/>
-      <c r="S19"/>
+      <c r="R19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S19" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4969,8 +6289,12 @@
       <c r="Q20" t="s">
         <v>281</v>
       </c>
-      <c r="R20"/>
-      <c r="S20"/>
+      <c r="R20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S20" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5024,8 +6348,12 @@
       <c r="Q21" t="s">
         <v>281</v>
       </c>
-      <c r="R21"/>
-      <c r="S21"/>
+      <c r="R21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S21" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5079,8 +6407,12 @@
       <c r="Q22" t="s">
         <v>281</v>
       </c>
-      <c r="R22"/>
-      <c r="S22"/>
+      <c r="R22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S22" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5134,8 +6466,12 @@
       <c r="Q23" t="s">
         <v>281</v>
       </c>
-      <c r="R23"/>
-      <c r="S23"/>
+      <c r="R23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S23" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5189,8 +6525,12 @@
       <c r="Q24" t="s">
         <v>281</v>
       </c>
-      <c r="R24"/>
-      <c r="S24"/>
+      <c r="R24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S24" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -5244,8 +6584,12 @@
       <c r="Q25" t="s">
         <v>281</v>
       </c>
-      <c r="R25"/>
-      <c r="S25"/>
+      <c r="R25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S25" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -5299,8 +6643,12 @@
       <c r="Q26" t="s">
         <v>281</v>
       </c>
-      <c r="R26"/>
-      <c r="S26"/>
+      <c r="R26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S26" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5354,8 +6702,12 @@
       <c r="Q27" t="s">
         <v>281</v>
       </c>
-      <c r="R27"/>
-      <c r="S27"/>
+      <c r="R27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S27" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5409,8 +6761,12 @@
       <c r="Q28" t="s">
         <v>281</v>
       </c>
-      <c r="R28"/>
-      <c r="S28"/>
+      <c r="R28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S28" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5464,8 +6820,12 @@
       <c r="Q29" t="s">
         <v>281</v>
       </c>
-      <c r="R29"/>
-      <c r="S29"/>
+      <c r="R29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S29" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5519,8 +6879,12 @@
       <c r="Q30" t="s">
         <v>281</v>
       </c>
-      <c r="R30"/>
-      <c r="S30"/>
+      <c r="R30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S30" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5574,8 +6938,12 @@
       <c r="Q31" t="s">
         <v>281</v>
       </c>
-      <c r="R31"/>
-      <c r="S31"/>
+      <c r="R31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S31" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5629,8 +6997,12 @@
       <c r="Q32" t="s">
         <v>281</v>
       </c>
-      <c r="R32"/>
-      <c r="S32"/>
+      <c r="R32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S32" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5684,8 +7056,12 @@
       <c r="Q33" t="s">
         <v>281</v>
       </c>
-      <c r="R33"/>
-      <c r="S33"/>
+      <c r="R33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S33" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5739,8 +7115,12 @@
       <c r="Q34" t="s">
         <v>281</v>
       </c>
-      <c r="R34"/>
-      <c r="S34"/>
+      <c r="R34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S34" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5794,8 +7174,12 @@
       <c r="Q35" t="s">
         <v>281</v>
       </c>
-      <c r="R35"/>
-      <c r="S35"/>
+      <c r="R35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S35" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5849,8 +7233,12 @@
       <c r="Q36" t="s">
         <v>281</v>
       </c>
-      <c r="R36"/>
-      <c r="S36"/>
+      <c r="R36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S36" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5904,8 +7292,12 @@
       <c r="Q37" t="s">
         <v>281</v>
       </c>
-      <c r="R37"/>
-      <c r="S37"/>
+      <c r="R37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S37" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5959,8 +7351,12 @@
       <c r="Q38" t="s">
         <v>281</v>
       </c>
-      <c r="R38"/>
-      <c r="S38"/>
+      <c r="R38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S38" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6014,8 +7410,12 @@
       <c r="Q39" t="s">
         <v>281</v>
       </c>
-      <c r="R39"/>
-      <c r="S39"/>
+      <c r="R39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S39" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6069,8 +7469,12 @@
       <c r="Q40" t="s">
         <v>281</v>
       </c>
-      <c r="R40"/>
-      <c r="S40"/>
+      <c r="R40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S40" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6124,8 +7528,12 @@
       <c r="Q41" t="s">
         <v>281</v>
       </c>
-      <c r="R41"/>
-      <c r="S41"/>
+      <c r="R41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S41" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6179,8 +7587,12 @@
       <c r="Q42" t="s">
         <v>281</v>
       </c>
-      <c r="R42"/>
-      <c r="S42"/>
+      <c r="R42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S42" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6234,8 +7646,12 @@
       <c r="Q43" t="s">
         <v>281</v>
       </c>
-      <c r="R43"/>
-      <c r="S43"/>
+      <c r="R43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S43" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6289,8 +7705,12 @@
       <c r="Q44" t="s">
         <v>281</v>
       </c>
-      <c r="R44"/>
-      <c r="S44"/>
+      <c r="R44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S44" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6344,8 +7764,12 @@
       <c r="Q45" t="s">
         <v>281</v>
       </c>
-      <c r="R45"/>
-      <c r="S45"/>
+      <c r="R45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S45" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6399,8 +7823,12 @@
       <c r="Q46" t="s">
         <v>281</v>
       </c>
-      <c r="R46"/>
-      <c r="S46"/>
+      <c r="R46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S46" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6454,8 +7882,12 @@
       <c r="Q47" t="s">
         <v>281</v>
       </c>
-      <c r="R47"/>
-      <c r="S47"/>
+      <c r="R47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S47" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6509,8 +7941,12 @@
       <c r="Q48" t="s">
         <v>281</v>
       </c>
-      <c r="R48"/>
-      <c r="S48"/>
+      <c r="R48" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S48" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6564,8 +8000,12 @@
       <c r="Q49" t="s">
         <v>281</v>
       </c>
-      <c r="R49"/>
-      <c r="S49"/>
+      <c r="R49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S49" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6619,8 +8059,12 @@
       <c r="Q50" t="s">
         <v>281</v>
       </c>
-      <c r="R50"/>
-      <c r="S50"/>
+      <c r="R50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S50" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6674,8 +8118,12 @@
       <c r="Q51" t="s">
         <v>281</v>
       </c>
-      <c r="R51"/>
-      <c r="S51"/>
+      <c r="R51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S51" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6729,8 +8177,12 @@
       <c r="Q52" t="s">
         <v>281</v>
       </c>
-      <c r="R52"/>
-      <c r="S52"/>
+      <c r="R52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S52" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6784,8 +8236,12 @@
       <c r="Q53" t="s">
         <v>281</v>
       </c>
-      <c r="R53"/>
-      <c r="S53"/>
+      <c r="R53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S53" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6839,8 +8295,12 @@
       <c r="Q54" t="s">
         <v>281</v>
       </c>
-      <c r="R54"/>
-      <c r="S54"/>
+      <c r="R54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S54" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6894,8 +8354,12 @@
       <c r="Q55" t="s">
         <v>281</v>
       </c>
-      <c r="R55"/>
-      <c r="S55"/>
+      <c r="R55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S55" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6949,8 +8413,12 @@
       <c r="Q56" t="s">
         <v>281</v>
       </c>
-      <c r="R56"/>
-      <c r="S56"/>
+      <c r="R56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S56" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7004,8 +8472,12 @@
       <c r="Q57" t="s">
         <v>281</v>
       </c>
-      <c r="R57"/>
-      <c r="S57"/>
+      <c r="R57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S57" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7059,8 +8531,12 @@
       <c r="Q58" t="s">
         <v>281</v>
       </c>
-      <c r="R58"/>
-      <c r="S58"/>
+      <c r="R58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S58" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7114,8 +8590,12 @@
       <c r="Q59" t="s">
         <v>281</v>
       </c>
-      <c r="R59"/>
-      <c r="S59"/>
+      <c r="R59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S59" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7169,8 +8649,12 @@
       <c r="Q60" t="s">
         <v>281</v>
       </c>
-      <c r="R60"/>
-      <c r="S60"/>
+      <c r="R60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S60" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7224,8 +8708,12 @@
       <c r="Q61" t="s">
         <v>281</v>
       </c>
-      <c r="R61"/>
-      <c r="S61"/>
+      <c r="R61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S61" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7279,8 +8767,12 @@
       <c r="Q62" t="s">
         <v>281</v>
       </c>
-      <c r="R62"/>
-      <c r="S62"/>
+      <c r="R62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S62" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7334,8 +8826,12 @@
       <c r="Q63" t="s">
         <v>281</v>
       </c>
-      <c r="R63"/>
-      <c r="S63"/>
+      <c r="R63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S63" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7389,8 +8885,12 @@
       <c r="Q64" t="s">
         <v>281</v>
       </c>
-      <c r="R64"/>
-      <c r="S64"/>
+      <c r="R64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S64" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7444,8 +8944,12 @@
       <c r="Q65" t="s">
         <v>281</v>
       </c>
-      <c r="R65"/>
-      <c r="S65"/>
+      <c r="R65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S65" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7499,8 +9003,12 @@
       <c r="Q66" t="s">
         <v>281</v>
       </c>
-      <c r="R66"/>
-      <c r="S66"/>
+      <c r="R66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S66" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7554,8 +9062,12 @@
       <c r="Q67" t="s">
         <v>281</v>
       </c>
-      <c r="R67"/>
-      <c r="S67"/>
+      <c r="R67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S67" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7609,8 +9121,12 @@
       <c r="Q68" t="s">
         <v>281</v>
       </c>
-      <c r="R68"/>
-      <c r="S68"/>
+      <c r="R68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S68" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7664,8 +9180,12 @@
       <c r="Q69" t="s">
         <v>281</v>
       </c>
-      <c r="R69"/>
-      <c r="S69"/>
+      <c r="R69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S69" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7719,8 +9239,12 @@
       <c r="Q70" t="s">
         <v>281</v>
       </c>
-      <c r="R70"/>
-      <c r="S70"/>
+      <c r="R70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S70" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7774,8 +9298,12 @@
       <c r="Q71" t="s">
         <v>281</v>
       </c>
-      <c r="R71"/>
-      <c r="S71"/>
+      <c r="R71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S71" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7829,8 +9357,12 @@
       <c r="Q72" t="s">
         <v>281</v>
       </c>
-      <c r="R72"/>
-      <c r="S72"/>
+      <c r="R72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S72" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7884,8 +9416,12 @@
       <c r="Q73" t="s">
         <v>281</v>
       </c>
-      <c r="R73"/>
-      <c r="S73"/>
+      <c r="R73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S73" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7939,8 +9475,12 @@
       <c r="Q74" t="s">
         <v>281</v>
       </c>
-      <c r="R74"/>
-      <c r="S74"/>
+      <c r="R74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S74" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7994,8 +9534,12 @@
       <c r="Q75" t="s">
         <v>281</v>
       </c>
-      <c r="R75"/>
-      <c r="S75"/>
+      <c r="R75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S75" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8049,8 +9593,12 @@
       <c r="Q76" t="s">
         <v>281</v>
       </c>
-      <c r="R76"/>
-      <c r="S76"/>
+      <c r="R76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S76" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8104,8 +9652,12 @@
       <c r="Q77" t="s">
         <v>281</v>
       </c>
-      <c r="R77"/>
-      <c r="S77"/>
+      <c r="R77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S77" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8159,8 +9711,12 @@
       <c r="Q78" t="s">
         <v>281</v>
       </c>
-      <c r="R78"/>
-      <c r="S78"/>
+      <c r="R78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S78" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8214,8 +9770,12 @@
       <c r="Q79" t="s">
         <v>281</v>
       </c>
-      <c r="R79"/>
-      <c r="S79"/>
+      <c r="R79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S79" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
